--- a/db-testing-tool/data/DRD_Open_Tax_Lots_non_bkr_Fact (1).xlsx
+++ b/db-testing-tool/data/DRD_Open_Tax_Lots_non_bkr_Fact (1).xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB403F4-62DF-48BA-A3DD-9C9C0C171AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DD3363-6007-46B2-B3AE-B2C669DD51D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="32190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="225" windowWidth="57840" windowHeight="32190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table-View" sheetId="13" r:id="rId1"/>
@@ -27755,33 +27755,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8889ac66-a331-4fe6-8d0f-c6fea2346e24">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd">
-      <UserInfo>
-        <DisplayName>Anand Waishampayan</DisplayName>
-        <AccountId>70</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100689FE176A865024B82746AC01372DAB6" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="922c480ddc59e6305a8a8fb3a8148c08">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8889ac66-a331-4fe6-8d0f-c6fea2346e24" xmlns:ns3="58a27bba-3e67-43d1-8504-e8ab049072dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7adf1aec20f105c257528873c177ef16" ns2:_="" ns3:_="">
     <xsd:import namespace="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
@@ -28030,10 +28003,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8889ac66-a331-4fe6-8d0f-c6fea2346e24">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="58a27bba-3e67-43d1-8504-e8ab049072dd">
+      <UserInfo>
+        <DisplayName>Anand Waishampayan</DisplayName>
+        <AccountId>70</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E513F4-A103-415D-B9AD-2F9B0BEDFF36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC84F7F3-77E9-4523-AFE1-BA9C3C1DDAE8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
+    <ds:schemaRef ds:uri="58a27bba-3e67-43d1-8504-e8ab049072dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -28050,20 +28061,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC84F7F3-77E9-4523-AFE1-BA9C3C1DDAE8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1E513F4-A103-415D-B9AD-2F9B0BEDFF36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8889ac66-a331-4fe6-8d0f-c6fea2346e24"/>
-    <ds:schemaRef ds:uri="58a27bba-3e67-43d1-8504-e8ab049072dd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>